--- a/data/lov-master.xlsx
+++ b/data/lov-master.xlsx
@@ -15076,42 +15076,45 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="4" t="inlineStr">
+      <c r="A345" t="inlineStr">
         <is>
           <t>AnchorageFoundation</t>
         </is>
       </c>
-      <c r="B345" s="4" t="inlineStr">
-        <is>
-          <t>U.S.</t>
-        </is>
-      </c>
-      <c r="C345" s="4" t="inlineStr"/>
-      <c r="D345" s="4" t="inlineStr"/>
-      <c r="E345" s="4" t="inlineStr"/>
-      <c r="F345" s="4" t="n"/>
-      <c r="G345" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H345" s="4" t="inlineStr">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>UNIQUE SOLUTION</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>AnUS</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I345" s="4" t="inlineStr"/>
-      <c r="J345" s="4" t="inlineStr">
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr">
         <is>
           <t>EP11A</t>
         </is>
       </c>
-      <c r="K345" s="4" t="n">
+      <c r="K345" t="n">
         <v>23</v>
       </c>
-      <c r="L345" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -24283,322 +24286,346 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="4" t="inlineStr">
+      <c r="A518" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B518" s="4" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>M3 Ø36</t>
         </is>
       </c>
-      <c r="C518" s="4" t="inlineStr"/>
-      <c r="D518" s="4" t="inlineStr"/>
-      <c r="E518" s="4" t="inlineStr"/>
-      <c r="F518" s="4" t="n"/>
-      <c r="G518" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H518" s="4" t="inlineStr">
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I518" s="4" t="inlineStr"/>
-      <c r="J518" s="4" t="inlineStr">
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
         <is>
           <t>EP11B, EP15</t>
         </is>
       </c>
-      <c r="K518" s="4" t="n">
+      <c r="K518" t="n">
         <v>67</v>
       </c>
-      <c r="L518" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="4" t="inlineStr">
+      <c r="A519" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B519" s="4" t="inlineStr">
+      <c r="B519" t="inlineStr">
         <is>
           <t>M3 Ø42</t>
         </is>
       </c>
-      <c r="C519" s="4" t="inlineStr"/>
-      <c r="D519" s="4" t="inlineStr"/>
-      <c r="E519" s="4" t="inlineStr"/>
-      <c r="F519" s="4" t="n"/>
-      <c r="G519" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H519" s="4" t="inlineStr">
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I519" s="4" t="inlineStr"/>
-      <c r="J519" s="4" t="inlineStr">
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
         <is>
           <t>EP11B</t>
         </is>
       </c>
-      <c r="K519" s="4" t="n">
+      <c r="K519" t="n">
         <v>1</v>
       </c>
-      <c r="L519" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="4" t="inlineStr">
+      <c r="A520" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B520" s="4" t="inlineStr">
+      <c r="B520" t="inlineStr">
         <is>
           <t>M5 Ø36</t>
         </is>
       </c>
-      <c r="C520" s="4" t="inlineStr"/>
-      <c r="D520" s="4" t="inlineStr"/>
-      <c r="E520" s="4" t="inlineStr"/>
-      <c r="F520" s="4" t="n"/>
-      <c r="G520" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H520" s="4" t="inlineStr">
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I520" s="4" t="inlineStr"/>
-      <c r="J520" s="4" t="inlineStr">
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
         <is>
           <t>EP11B</t>
         </is>
       </c>
-      <c r="K520" s="4" t="n">
+      <c r="K520" t="n">
         <v>1</v>
       </c>
-      <c r="L520" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="4" t="inlineStr">
+      <c r="A521" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B521" s="4" t="inlineStr">
+      <c r="B521" t="inlineStr">
         <is>
           <t>M5 Ø42</t>
         </is>
       </c>
-      <c r="C521" s="4" t="inlineStr"/>
-      <c r="D521" s="4" t="inlineStr"/>
-      <c r="E521" s="4" t="inlineStr"/>
-      <c r="F521" s="4" t="n"/>
-      <c r="G521" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H521" s="4" t="inlineStr">
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I521" s="4" t="inlineStr"/>
-      <c r="J521" s="4" t="inlineStr">
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
         <is>
           <t>EP11B, EP15</t>
         </is>
       </c>
-      <c r="K521" s="4" t="n">
+      <c r="K521" t="n">
         <v>34</v>
       </c>
-      <c r="L521" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="4" t="inlineStr">
+      <c r="A522" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B522" s="4" t="inlineStr">
+      <c r="B522" t="inlineStr">
         <is>
           <t>M6 Ø36</t>
         </is>
       </c>
-      <c r="C522" s="4" t="inlineStr"/>
-      <c r="D522" s="4" t="inlineStr"/>
-      <c r="E522" s="4" t="inlineStr"/>
-      <c r="F522" s="4" t="n"/>
-      <c r="G522" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H522" s="4" t="inlineStr">
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I522" s="4" t="inlineStr"/>
-      <c r="J522" s="4" t="inlineStr">
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
         <is>
           <t>EP11B</t>
         </is>
       </c>
-      <c r="K522" s="4" t="n">
+      <c r="K522" t="n">
         <v>6</v>
       </c>
-      <c r="L522" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="4" t="inlineStr">
+      <c r="A523" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B523" s="4" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>M6 Ø42</t>
         </is>
       </c>
-      <c r="C523" s="4" t="inlineStr"/>
-      <c r="D523" s="4" t="inlineStr"/>
-      <c r="E523" s="4" t="inlineStr"/>
-      <c r="F523" s="4" t="n"/>
-      <c r="G523" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H523" s="4" t="inlineStr">
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I523" s="4" t="inlineStr"/>
-      <c r="J523" s="4" t="inlineStr">
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
         <is>
           <t>EP11B, EP15</t>
         </is>
       </c>
-      <c r="K523" s="4" t="n">
+      <c r="K523" t="n">
         <v>32</v>
       </c>
-      <c r="L523" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="4" t="inlineStr">
+      <c r="A524" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B524" s="4" t="inlineStr">
+      <c r="B524" t="inlineStr">
         <is>
           <t>M7 Ø36</t>
         </is>
       </c>
-      <c r="C524" s="4" t="inlineStr"/>
-      <c r="D524" s="4" t="inlineStr"/>
-      <c r="E524" s="4" t="inlineStr"/>
-      <c r="F524" s="4" t="n"/>
-      <c r="G524" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H524" s="4" t="inlineStr">
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I524" s="4" t="inlineStr"/>
-      <c r="J524" s="4" t="inlineStr">
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
         <is>
           <t>EP15</t>
         </is>
       </c>
-      <c r="K524" s="4" t="n">
+      <c r="K524" t="n">
         <v>7</v>
       </c>
-      <c r="L524" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="4" t="inlineStr">
+      <c r="A525" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="B525" s="4" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>M8 Ø36</t>
         </is>
       </c>
-      <c r="C525" s="4" t="inlineStr"/>
-      <c r="D525" s="4" t="inlineStr"/>
-      <c r="E525" s="4" t="inlineStr"/>
-      <c r="F525" s="4" t="n"/>
-      <c r="G525" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H525" s="4" t="inlineStr">
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I525" s="4" t="inlineStr"/>
-      <c r="J525" s="4" t="inlineStr">
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr">
         <is>
           <t>EP15</t>
         </is>
       </c>
-      <c r="K525" s="4" t="n">
+      <c r="K525" t="n">
         <v>1</v>
       </c>
-      <c r="L525" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -32717,42 +32744,41 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" s="4" t="inlineStr">
+      <c r="A700" t="inlineStr">
         <is>
           <t>PoleType</t>
         </is>
       </c>
-      <c r="B700" s="4" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>UNIQUE SOLUTION</t>
         </is>
       </c>
-      <c r="C700" s="4" t="inlineStr"/>
-      <c r="D700" s="4" t="inlineStr"/>
-      <c r="E700" s="4" t="inlineStr"/>
-      <c r="F700" s="4" t="n"/>
-      <c r="G700" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H700" s="4" t="inlineStr">
+      <c r="C700" t="inlineStr"/>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" t="inlineStr"/>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
         <is>
           <t>TRACK</t>
         </is>
       </c>
-      <c r="I700" s="4" t="inlineStr"/>
-      <c r="J700" s="4" t="inlineStr">
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="inlineStr">
         <is>
           <t>EP7</t>
         </is>
       </c>
-      <c r="K700" s="4" t="n">
+      <c r="K700" t="n">
         <v>4</v>
       </c>
-      <c r="L700" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -45421,7 +45447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45504,12 +45530,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CXR_L</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pole foundation Type CX in L</t>
+          <t>Pole foundation with metric anchor bolts</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -45526,12 +45552,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>CXR_L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Base for pole in viaduct</t>
+          <t>Pole foundation Type CX in L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -45548,12 +45574,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Base for pole in Lateral wall</t>
+          <t>Base for pole in viaduct</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -45570,12 +45596,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WDX</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Base for pole with drainage</t>
+          <t>Base for pole in Lateral wall</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -45592,12 +45618,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WTX</t>
+          <t>WDX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Base for pole in Top wall</t>
+          <t>Base for pole with drainage</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -45609,17 +45635,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PortalType</t>
+          <t>FoundationType</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PR1X</t>
+          <t>WTX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portal type X</t>
+          <t>Base for pole in Top wall</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -45636,12 +45662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SP1R</t>
+          <t>PR1X</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Semi Portal</t>
+          <t>Portal type X</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -45658,12 +45684,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>SP1R</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Semi Portal type B7</t>
+          <t>Semi Portal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -45680,12 +45706,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEADSPAN</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Headspan</t>
+          <t>Semi Portal type B7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -45702,12 +45728,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GANTRY</t>
+          <t>HEADSPAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gantry</t>
+          <t>Headspan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -45719,17 +45745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AnchorageFoundationType</t>
+          <t>PortalType</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AnMC</t>
+          <t>GANTRY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Messenger and contact wire anchorage foundation</t>
+          <t>Gantry</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -45746,15 +45772,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>AnMC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Messenger and contact wire anchorage foundation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AnchorageFoundationType</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AnUS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unique solution - bespoke anchorage foundation supplied separately</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AnchorageFoundationType</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>AnM</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Return, Feeder and Midpoint anchorage foundation</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>SI</t>
         </is>

--- a/data/lov-master.xlsx
+++ b/data/lov-master.xlsx
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L822"/>
+  <dimension ref="A1:L820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -37551,82 +37551,84 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="4" t="inlineStr">
+      <c r="A783" t="inlineStr">
         <is>
           <t>DisconnectorFunction</t>
         </is>
       </c>
-      <c r="B783" s="4" t="inlineStr">
-        <is>
-          <t>Disc-pp</t>
-        </is>
-      </c>
-      <c r="C783" s="4" t="inlineStr"/>
-      <c r="D783" s="4" t="inlineStr"/>
-      <c r="E783" s="4" t="inlineStr"/>
-      <c r="F783" s="4" t="n"/>
-      <c r="G783" s="4" t="inlineStr">
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Disc-pr</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr"/>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr"/>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>EP11A, EP4, EP5, EP7, EP9A, EP9B</t>
+        </is>
+      </c>
+      <c r="K783" t="n">
+        <v>30</v>
+      </c>
+      <c r="L783" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H783" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I783" s="4" t="inlineStr"/>
-      <c r="J783" s="4" t="inlineStr">
-        <is>
-          <t>EP9A</t>
-        </is>
-      </c>
-      <c r="K783" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L783" s="4" t="inlineStr">
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>DisconnectorFunction</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Disc/IO</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Insulated Overlap disconnector</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr"/>
+      <c r="G784" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-    </row>
-    <row r="784">
-      <c r="A784" s="4" t="inlineStr">
-        <is>
-          <t>DisconnectorFunction</t>
-        </is>
-      </c>
-      <c r="B784" s="4" t="inlineStr">
-        <is>
-          <t>Disc-pr</t>
-        </is>
-      </c>
-      <c r="C784" s="4" t="inlineStr"/>
-      <c r="D784" s="4" t="inlineStr"/>
-      <c r="E784" s="4" t="inlineStr"/>
-      <c r="F784" s="4" t="n"/>
-      <c r="G784" s="4" t="inlineStr">
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+        </is>
+      </c>
+      <c r="K784" t="n">
+        <v>96</v>
+      </c>
+      <c r="L784" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="H784" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I784" s="4" t="inlineStr"/>
-      <c r="J784" s="4" t="inlineStr">
-        <is>
-          <t>EP11A, EP4, EP5, EP7, EP9B</t>
-        </is>
-      </c>
-      <c r="K784" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="L784" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -37638,14 +37640,10 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Disc/IO</t>
-        </is>
-      </c>
-      <c r="C785" t="inlineStr">
-        <is>
-          <t>Insulated Overlap disconnector</t>
-        </is>
-      </c>
+          <t>Disc/IO-pr</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
@@ -37655,17 +37653,17 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>LEGEND+TRACK</t>
+          <t>TRACK</t>
         </is>
       </c>
       <c r="I785" t="inlineStr"/>
       <c r="J785" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP11B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K785" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -37674,42 +37672,45 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="4" t="inlineStr">
+      <c r="A786" t="inlineStr">
         <is>
           <t>DisconnectorFunction</t>
         </is>
       </c>
-      <c r="B786" s="4" t="inlineStr">
-        <is>
-          <t>Disc/IO-pr</t>
-        </is>
-      </c>
-      <c r="C786" s="4" t="inlineStr"/>
-      <c r="D786" s="4" t="inlineStr"/>
-      <c r="E786" s="4" t="inlineStr"/>
-      <c r="F786" s="4" t="n"/>
-      <c r="G786" s="4" t="inlineStr">
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Disc/NS</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Neutral Section disconnector</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr"/>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>EP11A, EP11B, EP4, EP5, EP7, EP9A, EP9B</t>
+        </is>
+      </c>
+      <c r="K786" t="n">
+        <v>11</v>
+      </c>
+      <c r="L786" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="H786" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I786" s="4" t="inlineStr"/>
-      <c r="J786" s="4" t="inlineStr">
-        <is>
-          <t>EP11B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
-        </is>
-      </c>
-      <c r="K786" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="L786" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -37721,14 +37722,10 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Disc/NS</t>
-        </is>
-      </c>
-      <c r="C787" t="inlineStr">
-        <is>
-          <t>Neutral Section disconnector</t>
-        </is>
-      </c>
+          <t>Disc/PP</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
@@ -37738,17 +37735,17 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>LEGEND+TRACK</t>
+          <t>TRACK</t>
         </is>
       </c>
       <c r="I787" t="inlineStr"/>
       <c r="J787" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP4, EP5, EP7, EP9A, EP9B</t>
+          <t>EP11B, EP14A, EP14B, EP15, EP5, EP6, EP7, EP9B</t>
         </is>
       </c>
       <c r="K787" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -37764,7 +37761,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Disc/PP</t>
+          <t>Disc/PP-pr</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -37783,11 +37780,11 @@
       <c r="I788" t="inlineStr"/>
       <c r="J788" t="inlineStr">
         <is>
-          <t>EP11B, EP14A, EP14B, EP15, EP5, EP6, EP7, EP9B</t>
+          <t>EP11B, EP5, EP6, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K788" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -37796,42 +37793,45 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="4" t="inlineStr">
+      <c r="A789" t="inlineStr">
         <is>
           <t>DisconnectorFunction</t>
         </is>
       </c>
-      <c r="B789" s="4" t="inlineStr">
-        <is>
-          <t>Disc/PP-pr</t>
-        </is>
-      </c>
-      <c r="C789" s="4" t="inlineStr"/>
-      <c r="D789" s="4" t="inlineStr"/>
-      <c r="E789" s="4" t="inlineStr"/>
-      <c r="F789" s="4" t="n"/>
-      <c r="G789" s="4" t="inlineStr">
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Disc/SI</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Section Insulator disconnector</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr"/>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>EP11A, EP4, EP5, EP7, EP9B</t>
+        </is>
+      </c>
+      <c r="K789" t="n">
+        <v>20</v>
+      </c>
+      <c r="L789" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="H789" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I789" s="4" t="inlineStr"/>
-      <c r="J789" s="4" t="inlineStr">
-        <is>
-          <t>EP11B, EP5, EP6, EP9A, EP9B</t>
-        </is>
-      </c>
-      <c r="K789" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L789" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -37843,14 +37843,10 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Disc/SI</t>
-        </is>
-      </c>
-      <c r="C790" t="inlineStr">
-        <is>
-          <t>Section Insulator disconnector</t>
-        </is>
-      </c>
+          <t>Disc/SI-pr</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr"/>
       <c r="G790" t="inlineStr">
@@ -37860,17 +37856,17 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>LEGEND+TRACK</t>
+          <t>TRACK</t>
         </is>
       </c>
       <c r="I790" t="inlineStr"/>
       <c r="J790" t="inlineStr">
         <is>
-          <t>EP11A, EP4, EP5, EP7, EP9B</t>
+          <t>EP9B</t>
         </is>
       </c>
       <c r="K790" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -37879,42 +37875,56 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="4" t="inlineStr">
+      <c r="A791" t="inlineStr">
         <is>
           <t>DisconnectorFunction</t>
         </is>
       </c>
-      <c r="B791" s="4" t="inlineStr">
-        <is>
-          <t>Disc/SI-pr</t>
-        </is>
-      </c>
-      <c r="C791" s="4" t="inlineStr"/>
-      <c r="D791" s="4" t="inlineStr"/>
-      <c r="E791" s="4" t="inlineStr"/>
-      <c r="F791" s="4" t="n"/>
-      <c r="G791" s="4" t="inlineStr">
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Disc/t</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Disconnector 3 colums 25 KV 2500 A</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Seccionador monopolar de AV apertura vertical</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="n">
+        <v>6172</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>BOQ+LEGEND</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>DISCONNECTORS ASSEMBLIES, SECCIONADORES</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+        </is>
+      </c>
+      <c r="K791" t="n">
+        <v>0</v>
+      </c>
+      <c r="L791" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="H791" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I791" s="4" t="inlineStr"/>
-      <c r="J791" s="4" t="inlineStr">
-        <is>
-          <t>EP9B</t>
-        </is>
-      </c>
-      <c r="K791" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L791" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -37926,23 +37936,20 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Disc/t</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Disconnector 3 colums 25 KV 2500 A</t>
+          <t>Connections of Disconnector &amp; Earthing Device in same plo</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Seccionador monopolar de AV apertura vertical</t>
+          <t>Aparellaje de Earthing Device en poste (Sin feeder)</t>
         </is>
       </c>
       <c r="E792" t="inlineStr"/>
-      <c r="F792" t="n">
-        <v>6172</v>
-      </c>
       <c r="G792" t="inlineStr">
         <is>
           <t>SI</t>
@@ -37950,12 +37957,12 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND</t>
+          <t>BOQ+LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>DISCONNECTORS ASSEMBLIES, SECCIONADORES</t>
+          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
@@ -37964,7 +37971,7 @@
         </is>
       </c>
       <c r="K792" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -37980,17 +37987,17 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>ED+Disc</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Connections of Disconnector &amp; Earthing Device in same plo</t>
+          <t>Connections of Disconnector for feeder TS connection 1 track with wire</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Aparellaje de Earthing Device en poste (Sin feeder)</t>
+          <t>Aparellaje de conjunto de seccionador monopolar y Earthing Device en mismo poste (Sin feeder)</t>
         </is>
       </c>
       <c r="E793" t="inlineStr"/>
@@ -38001,7 +38008,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
+          <t>BOQ</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -38015,7 +38022,7 @@
         </is>
       </c>
       <c r="K793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -38031,20 +38038,23 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ED+Disc</t>
+          <t>ED/T</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Connections of Disconnector for feeder TS connection 1 track with wire</t>
+          <t>Connections of Earthing Device in tunnel</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Aparellaje de conjunto de seccionador monopolar y Earthing Device en mismo poste (Sin feeder)</t>
+          <t>Aparellaje de dispositivo de puesta a tierra en túnel</t>
         </is>
       </c>
       <c r="E794" t="inlineStr"/>
+      <c r="F794" t="n">
+        <v>6173</v>
+      </c>
       <c r="G794" t="inlineStr">
         <is>
           <t>SI</t>
@@ -38052,7 +38062,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>BOQ</t>
+          <t>BOQ+LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -38066,7 +38076,7 @@
         </is>
       </c>
       <c r="K794" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
@@ -38082,22 +38092,22 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>ED/T</t>
+          <t>FS-1</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Connections of Earthing Device in tunnel</t>
+          <t>Connections of Disconnector for feeder TS connection 1 track with cable</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Aparellaje de dispositivo de puesta a tierra en túnel</t>
+          <t>Aparellaje para acometida de feeder en poste para 1 vía (incluido paso aislado a desnudo)</t>
         </is>
       </c>
       <c r="E795" t="inlineStr"/>
       <c r="F795" t="n">
-        <v>6173</v>
+        <v>6175</v>
       </c>
       <c r="G795" t="inlineStr">
         <is>
@@ -38120,7 +38130,7 @@
         </is>
       </c>
       <c r="K795" t="n">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
@@ -38136,23 +38146,20 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>FS-1</t>
+          <t>FS-1D</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Connections of Disconnector for feeder TS connection 1 track with cable</t>
+          <t>Connections of Load Breaker with earth connection for feeder connection 1 track with cable ¿?</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Aparellaje para acometida de feeder en poste para 1 vía (incluido paso aislado a desnudo)</t>
+          <t>Aparellaje para acometida de feeder a depot (incluido paso aislado a desnudo con pat y bajada a tierra)</t>
         </is>
       </c>
       <c r="E796" t="inlineStr"/>
-      <c r="F796" t="n">
-        <v>6175</v>
-      </c>
       <c r="G796" t="inlineStr">
         <is>
           <t>SI</t>
@@ -38160,7 +38167,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
+          <t>BOQ+LEGEND</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -38174,7 +38181,7 @@
         </is>
       </c>
       <c r="K796" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -38190,17 +38197,17 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>FS-1D</t>
+          <t>FS/1D</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Connections of Load Breaker with earth connection for feeder connection 1 track with cable ¿?</t>
+          <t>Load Breaker 25 KV 2500 A with vacuun chamber with Earth Connection</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Aparellaje para acometida de feeder a depot (incluido paso aislado a desnudo con pat y bajada a tierra)</t>
+          <t>Seccionador monopolar de AC con PAT</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
@@ -38211,12 +38218,12 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND</t>
+          <t>BOQ</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
+          <t>DISCONNECTORS ASSEMBLIES, SECCIONADORES</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
@@ -38241,17 +38248,17 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>FS/1D</t>
+          <t>FS/PP-1</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Load Breaker 25 KV 2500 A with vacuun chamber with Earth Connection</t>
+          <t>Connections of Disconnector for feeder TS connection 1 track with wire</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>Seccionador monopolar de AC con PAT</t>
+          <t>Aparellaje de seccionador de alimentacion para 1 via con cable desnudo.</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
@@ -38267,12 +38274,12 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>DISCONNECTORS ASSEMBLIES, SECCIONADORES</t>
+          <t>DISCONNECTORS ASSEMBLIES</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP11A, EP4, EP5, EP7</t>
         </is>
       </c>
       <c r="K798" t="n">
@@ -38292,7 +38299,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>FS/PP-1</t>
+          <t>FS/PP-2</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -38302,10 +38309,13 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Aparellaje de seccionador de alimentacion para 1 via con cable desnudo.</t>
+          <t>Aparellaje de pórtico de alimentación (ssee) y puesta en paralelo de 2 vías</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
+      <c r="F799" t="n">
+        <v>6176</v>
+      </c>
       <c r="G799" t="inlineStr">
         <is>
           <t>SI</t>
@@ -38313,21 +38323,21 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>BOQ</t>
+          <t>BOQ+LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>DISCONNECTORS ASSEMBLIES</t>
+          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>EP11A, EP4, EP5, EP7</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K799" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -38343,22 +38353,22 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>FS/PP-2</t>
+          <t>FS/PP-3</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Connections of Disconnector for feeder TS connection 1 track with wire</t>
+          <t>Connections of TS feeding portal for 3 tracks</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Aparellaje de pórtico de alimentación (ssee) y puesta en paralelo de 2 vías</t>
+          <t>Aparellaje de pórtico de alimentación (ssee) y puesta en paralelo de 3 vías</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="n">
-        <v>6176</v>
+        <v>6177</v>
       </c>
       <c r="G800" t="inlineStr">
         <is>
@@ -38367,7 +38377,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
+          <t>BOQ+LEGEND</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -38381,7 +38391,7 @@
         </is>
       </c>
       <c r="K800" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -38397,23 +38407,12 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>FS/PP-3</t>
-        </is>
-      </c>
-      <c r="C801" t="inlineStr">
-        <is>
-          <t>Connections of TS feeding portal for 3 tracks</t>
-        </is>
-      </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>Aparellaje de pórtico de alimentación (ssee) y puesta en paralelo de 3 vías</t>
-        </is>
-      </c>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr"/>
+      <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
-      <c r="F801" t="n">
-        <v>6177</v>
-      </c>
       <c r="G801" t="inlineStr">
         <is>
           <t>SI</t>
@@ -38421,21 +38420,17 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND</t>
-        </is>
-      </c>
-      <c r="I801" t="inlineStr">
-        <is>
-          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
-        </is>
-      </c>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr"/>
       <c r="J801" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP9A</t>
         </is>
       </c>
       <c r="K801" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -38451,7 +38446,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>FW-25</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
@@ -38470,11 +38465,11 @@
       <c r="I802" t="inlineStr"/>
       <c r="J802" t="inlineStr">
         <is>
-          <t>EP9A</t>
+          <t>EP4, EP5, EP6, EP9A</t>
         </is>
       </c>
       <c r="K802" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
@@ -38490,7 +38485,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>FW-25</t>
+          <t>FW-D</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -38509,11 +38504,11 @@
       <c r="I803" t="inlineStr"/>
       <c r="J803" t="inlineStr">
         <is>
-          <t>EP4, EP5, EP6, EP9A</t>
+          <t>EP9A, EP9B</t>
         </is>
       </c>
       <c r="K803" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -38529,7 +38524,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>FW-D</t>
+          <t>FW-DV</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -38548,11 +38543,11 @@
       <c r="I804" t="inlineStr"/>
       <c r="J804" t="inlineStr">
         <is>
-          <t>EP9A, EP9B</t>
+          <t>EP9B</t>
         </is>
       </c>
       <c r="K804" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -38568,10 +38563,14 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>FW-DV</t>
-        </is>
-      </c>
-      <c r="C805" t="inlineStr"/>
+          <t>LoadB</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Load Breaker</t>
+        </is>
+      </c>
       <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr"/>
       <c r="G805" t="inlineStr">
@@ -38581,17 +38580,17 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>TRACK</t>
+          <t>LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I805" t="inlineStr"/>
       <c r="J805" t="inlineStr">
         <is>
-          <t>EP9B</t>
+          <t>EP11A, EP4, EP5, EP6, EP7, EP9B</t>
         </is>
       </c>
       <c r="K805" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -38607,14 +38606,10 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>LoadB</t>
-        </is>
-      </c>
-      <c r="C806" t="inlineStr">
-        <is>
-          <t>Load Breaker</t>
-        </is>
-      </c>
+          <t>LoadB-pr</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="G806" t="inlineStr">
@@ -38624,17 +38619,17 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>LEGEND+TRACK</t>
+          <t>TRACK</t>
         </is>
       </c>
       <c r="I806" t="inlineStr"/>
       <c r="J806" t="inlineStr">
         <is>
-          <t>EP11A, EP4, EP5, EP6, EP7, EP9B</t>
+          <t>EP11A, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K806" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -38643,82 +38638,92 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" s="4" t="inlineStr">
+      <c r="A807" t="inlineStr">
         <is>
           <t>DisconnectorFunction</t>
         </is>
       </c>
-      <c r="B807" s="4" t="inlineStr">
-        <is>
-          <t>LoadB-pp</t>
-        </is>
-      </c>
-      <c r="C807" s="4" t="inlineStr"/>
-      <c r="D807" s="4" t="inlineStr"/>
-      <c r="E807" s="4" t="inlineStr"/>
-      <c r="F807" s="4" t="n"/>
-      <c r="G807" s="4" t="inlineStr">
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>LoadB/ED</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr"/>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>EP9B</t>
+        </is>
+      </c>
+      <c r="K807" t="n">
+        <v>5</v>
+      </c>
+      <c r="L807" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H807" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I807" s="4" t="inlineStr"/>
-      <c r="J807" s="4" t="inlineStr">
-        <is>
-          <t>EP9A</t>
-        </is>
-      </c>
-      <c r="K807" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L807" s="4" t="inlineStr">
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>DisconnectorFunction</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>LoadB/IO</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Insulated Overlap Load Breaker</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder) para seccionamiento de Lámina de aire</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="G808" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-    </row>
-    <row r="808">
-      <c r="A808" s="4" t="inlineStr">
-        <is>
-          <t>DisconnectorFunction</t>
-        </is>
-      </c>
-      <c r="B808" s="4" t="inlineStr">
-        <is>
-          <t>LoadB-pr</t>
-        </is>
-      </c>
-      <c r="C808" s="4" t="inlineStr"/>
-      <c r="D808" s="4" t="inlineStr"/>
-      <c r="E808" s="4" t="inlineStr"/>
-      <c r="F808" s="4" t="n"/>
-      <c r="G808" s="4" t="inlineStr">
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>BOQ+LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+        </is>
+      </c>
+      <c r="K808" t="n">
+        <v>113</v>
+      </c>
+      <c r="L808" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="H808" s="4" t="inlineStr">
-        <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I808" s="4" t="inlineStr"/>
-      <c r="J808" s="4" t="inlineStr">
-        <is>
-          <t>EP11A, EP7, EP9B</t>
-        </is>
-      </c>
-      <c r="K808" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L808" s="4" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -38730,11 +38735,15 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>LoadB/ED</t>
+          <t>LoadB/IO-pr</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
-      <c r="D809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Aparellaje tipo de conjunto de seccionador monopolar AC en portico para Seccionamiento de lámina de aire</t>
+        </is>
+      </c>
       <c r="E809" t="inlineStr"/>
       <c r="G809" t="inlineStr">
         <is>
@@ -38743,17 +38752,21 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I809" t="inlineStr"/>
+          <t>BOQ+TRACK</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
+        </is>
+      </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>EP9B</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K809" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
@@ -38769,17 +38782,17 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>LoadB/IO</t>
+          <t>LoadB/NS</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Insulated Overlap Load Breaker</t>
+          <t>Neutral Section Load Breaker</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder) para seccionamiento de Lámina de aire</t>
+          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder) para seccionamiento de zona neutra</t>
         </is>
       </c>
       <c r="E810" t="inlineStr"/>
@@ -38800,11 +38813,11 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K810" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -38820,13 +38833,17 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>LoadB/IO-pr</t>
-        </is>
-      </c>
-      <c r="C811" t="inlineStr"/>
+          <t>LoadB/PP</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Connections of Load Breaker (without feeder)</t>
+        </is>
+      </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Aparellaje tipo de conjunto de seccionador monopolar AC en portico para Seccionamiento de lámina de aire</t>
+          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder)</t>
         </is>
       </c>
       <c r="E811" t="inlineStr"/>
@@ -38837,7 +38854,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>BOQ+TRACK</t>
+          <t>BOQ+LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -38847,11 +38864,11 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K811" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -38867,17 +38884,17 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>LoadB/NS</t>
+          <t>LoadB/PP-pr</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Neutral Section Load Breaker</t>
+          <t>Connections of Load Breaker in OCS portal (without feeder)</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder) para seccionamiento de zona neutra</t>
+          <t>Aparellaje tipo de conjunto de seccionador monopolar AC en portico Catenaria Estacion</t>
         </is>
       </c>
       <c r="E812" t="inlineStr"/>
@@ -38888,7 +38905,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
+          <t>BOQ+TRACK</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -38898,11 +38915,11 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K812" t="n">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -38918,19 +38935,11 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>LoadB/PP</t>
-        </is>
-      </c>
-      <c r="C813" t="inlineStr">
-        <is>
-          <t>Connections of Load Breaker (without feeder)</t>
-        </is>
-      </c>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>Aparellaje de conjunto de seccionador monopolar AC en poste (Sin feeder)</t>
-        </is>
-      </c>
+          <t>LoadB/t</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
@@ -38939,21 +38948,17 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
-        </is>
-      </c>
-      <c r="I813" t="inlineStr">
-        <is>
-          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
-        </is>
-      </c>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr"/>
       <c r="J813" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP15</t>
         </is>
       </c>
       <c r="K813" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -38969,19 +38974,11 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>LoadB/PP-pr</t>
-        </is>
-      </c>
-      <c r="C814" t="inlineStr">
-        <is>
-          <t>Connections of Load Breaker in OCS portal (without feeder)</t>
-        </is>
-      </c>
-      <c r="D814" t="inlineStr">
-        <is>
-          <t>Aparellaje tipo de conjunto de seccionador monopolar AC en portico Catenaria Estacion</t>
-        </is>
-      </c>
+          <t>MW/CW-ISusp</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr"/>
       <c r="G814" t="inlineStr">
         <is>
@@ -38990,21 +38987,17 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>BOQ+TRACK</t>
-        </is>
-      </c>
-      <c r="I814" t="inlineStr">
-        <is>
-          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
-        </is>
-      </c>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr"/>
       <c r="J814" t="inlineStr">
         <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
+          <t>EP6</t>
         </is>
       </c>
       <c r="K814" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -39020,12 +39013,23 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>LoadB/t</t>
-        </is>
-      </c>
-      <c r="C815" t="inlineStr"/>
-      <c r="D815" t="inlineStr"/>
+          <t>PP-2</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Connections of paralelling portal for 2 tracks</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Aparellaje de puesta en paralelo de dos vías, i. transversales</t>
+        </is>
+      </c>
       <c r="E815" t="inlineStr"/>
+      <c r="F815" t="n">
+        <v>6179</v>
+      </c>
       <c r="G815" t="inlineStr">
         <is>
           <t>SI</t>
@@ -39033,17 +39037,21 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>TRACK</t>
-        </is>
-      </c>
-      <c r="I815" t="inlineStr"/>
+          <t>BOQ+LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
+        </is>
+      </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>EP15</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K815" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -39059,10 +39067,14 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>MW/CW-ISusp</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr"/>
+          <t>PP-3</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Paralleling post 3 tracks</t>
+        </is>
+      </c>
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr"/>
       <c r="G816" t="inlineStr">
@@ -39072,17 +39084,17 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>TRACK</t>
+          <t>LEGEND</t>
         </is>
       </c>
       <c r="I816" t="inlineStr"/>
       <c r="J816" t="inlineStr">
         <is>
-          <t>EP6</t>
+          <t>EP11A, EP4, EP5, EP7, EP9B</t>
         </is>
       </c>
       <c r="K816" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -39098,22 +39110,22 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>PP-2</t>
+          <t>PP-4</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Connections of paralelling portal for 2 tracks</t>
+          <t>Connections of paralelling portal for 4 tracks</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Aparellaje de puesta en paralelo de dos vías, i. transversales</t>
+          <t>Aparellaje de pórtico de puesta en paralelo de 4 vías</t>
         </is>
       </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="n">
-        <v>6179</v>
+        <v>6178</v>
       </c>
       <c r="G817" t="inlineStr">
         <is>
@@ -39122,7 +39134,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND+TRACK</t>
+          <t>BOQ+LEGEND</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -39136,7 +39148,7 @@
         </is>
       </c>
       <c r="K817" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L817" t="inlineStr">
         <is>
@@ -39152,12 +39164,12 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>PP-3</t>
+          <t>SECT-I</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Paralleling post 3 tracks</t>
+          <t>Section Insulator</t>
         </is>
       </c>
       <c r="D818" t="inlineStr"/>
@@ -39169,17 +39181,17 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>LEGEND</t>
+          <t>LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I818" t="inlineStr"/>
       <c r="J818" t="inlineStr">
         <is>
-          <t>EP11A, EP4, EP5, EP7, EP9B</t>
+          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K818" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -39195,22 +39207,22 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>PP-4</t>
+          <t>SurgeA</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Connections of paralelling portal for 4 tracks</t>
+          <t>Equipotential Surface for Portal 5m</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Aparellaje de pórtico de puesta en paralelo de 4 vías</t>
+          <t>Conjunto de autoválvula</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>6178</v>
+        <v>6684</v>
       </c>
       <c r="G819" t="inlineStr">
         <is>
@@ -39219,12 +39231,12 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>BOQ+LEGEND</t>
+          <t>BOQ+LEGEND+TRACK</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>APARELLAJES, DISCONNECTORS ASSEMBLIES</t>
+          <t>AUTOVALV., DISCONNECTORS ASSEMBLIES</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
@@ -39233,7 +39245,7 @@
         </is>
       </c>
       <c r="K819" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -39249,15 +39261,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>SECT-I</t>
+          <t>VoltageD</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Section Insulator</t>
-        </is>
-      </c>
-      <c r="D820" t="inlineStr"/>
+          <t>Voltage Detector</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Detector de tensión de 25 kV</t>
+        </is>
+      </c>
       <c r="E820" t="inlineStr"/>
       <c r="G820" t="inlineStr">
         <is>
@@ -39266,124 +39282,23 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>LEGEND+TRACK</t>
-        </is>
-      </c>
-      <c r="I820" t="inlineStr"/>
+          <t>BOQ+LEGEND+TRACK</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>AUTOVALV., DISCONNECTORS ASSEMBLIES</t>
+        </is>
+      </c>
       <c r="J820" t="inlineStr">
         <is>
           <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
         </is>
       </c>
       <c r="K820" t="n">
-        <v>298</v>
+        <v>145</v>
       </c>
       <c r="L820" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>DisconnectorFunction</t>
-        </is>
-      </c>
-      <c r="B821" t="inlineStr">
-        <is>
-          <t>SurgeA</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>Equipotential Surface for Portal 5m</t>
-        </is>
-      </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>Conjunto de autoválvula</t>
-        </is>
-      </c>
-      <c r="E821" t="inlineStr"/>
-      <c r="F821" t="n">
-        <v>6684</v>
-      </c>
-      <c r="G821" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H821" t="inlineStr">
-        <is>
-          <t>BOQ+LEGEND+TRACK</t>
-        </is>
-      </c>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>AUTOVALV., DISCONNECTORS ASSEMBLIES</t>
-        </is>
-      </c>
-      <c r="J821" t="inlineStr">
-        <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
-        </is>
-      </c>
-      <c r="K821" t="n">
-        <v>10</v>
-      </c>
-      <c r="L821" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>DisconnectorFunction</t>
-        </is>
-      </c>
-      <c r="B822" t="inlineStr">
-        <is>
-          <t>VoltageD</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>Voltage Detector</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>Detector de tensión de 25 kV</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr"/>
-      <c r="G822" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>BOQ+LEGEND+TRACK</t>
-        </is>
-      </c>
-      <c r="I822" t="inlineStr">
-        <is>
-          <t>AUTOVALV., DISCONNECTORS ASSEMBLIES</t>
-        </is>
-      </c>
-      <c r="J822" t="inlineStr">
-        <is>
-          <t>EP11A, EP11B, EP14A, EP14B, EP15, EP4, EP5, EP6, EP7, EP9A, EP9B</t>
-        </is>
-      </c>
-      <c r="K822" t="n">
-        <v>145</v>
-      </c>
-      <c r="L822" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
